--- a/Weighted average tariffs on chinese prod.xlsx
+++ b/Weighted average tariffs on chinese prod.xlsx
@@ -1,16 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fileVersion appName="SpreadsheetGear 7.1.1.120"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/52a34f2960585944/Documents/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EAECBBCD-A333-488B-9B07-303280BF0634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18075" windowHeight="9900" activeTab="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Product-TimeSeries-Product" sheetId="2" r:id="rId2"/>
+    <sheet name="Product-TimeSeries-Product" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="40001"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -143,136 +148,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="17">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Cambria"/>
-      <family val="2"/>
-      <scheme val="major"/>
     </font>
   </fonts>
   <fills count="2">
@@ -301,6 +184,16 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -588,1124 +481,1115 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P22"/>
-  <sheetFormatPr defaultRowHeight="12.75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.359375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.23046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.6796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.60546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="16" width="11.484375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="16" width="11.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row>
-      <c t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c t="s">
+      <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c t="s">
+      <c r="E1" t="s">
         <v>4</v>
       </c>
-      <c t="s">
+      <c r="F1" t="s">
         <v>5</v>
       </c>
-      <c t="s">
+      <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c t="s">
+      <c r="H1" t="s">
         <v>7</v>
       </c>
-      <c t="s">
+      <c r="I1" t="s">
         <v>8</v>
       </c>
-      <c t="s">
+      <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c t="s">
+      <c r="K1" t="s">
         <v>10</v>
       </c>
-      <c t="s">
+      <c r="L1" t="s">
         <v>11</v>
       </c>
-      <c t="s">
+      <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c t="s">
+      <c r="N1" t="s">
         <v>13</v>
       </c>
-      <c t="s">
+      <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c t="s">
+      <c r="P1" t="s">
         <v>15</v>
       </c>
     </row>
-    <row>
-      <c t="s">
-        <v>16</v>
-      </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-      <c t="s">
-        <v>18</v>
-      </c>
-      <c t="s">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" t="s">
         <v>19</v>
       </c>
-      <c t="s">
-        <v>20</v>
-      </c>
-      <c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2">
         <v>5.1258286837751887</v>
       </c>
-      <c>
+      <c r="G2">
         <v>5.648380090755138</v>
       </c>
-      <c>
+      <c r="H2">
         <v>5.971067292636052</v>
       </c>
-      <c>
+      <c r="I2">
         <v>5.9260464435086195</v>
       </c>
-      <c>
+      <c r="J2">
         <v>5.9047621794828018</v>
       </c>
-      <c>
+      <c r="K2">
         <v>33.259664670613965</v>
       </c>
-      <c>
+      <c r="L2">
         <v>31.160125512019125</v>
       </c>
-      <c>
+      <c r="M2">
         <v>6.2271611390284249</v>
       </c>
-      <c>
+      <c r="N2">
         <v>6.4789219235653368</v>
       </c>
-      <c>
+      <c r="O2">
         <v>6.5466969068390872</v>
       </c>
-      <c>
+      <c r="P2">
         <v>7.4973661283813877</v>
       </c>
     </row>
-    <row>
-      <c t="s">
-        <v>16</v>
-      </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-      <c t="s">
-        <v>18</v>
-      </c>
-      <c t="s">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" t="s">
         <v>21</v>
       </c>
-      <c t="s">
-        <v>20</v>
-      </c>
-      <c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3">
         <v>2.5630878287422725</v>
       </c>
-      <c>
+      <c r="G3">
         <v>2.6554439973903565</v>
       </c>
-      <c>
+      <c r="H3">
         <v>2.5548374025955956</v>
       </c>
-      <c>
+      <c r="I3">
         <v>2.6087661373692073</v>
       </c>
-      <c>
+      <c r="J3">
         <v>2.6932181499691192</v>
       </c>
-      <c>
+      <c r="K3">
         <v>2.4588832717421436</v>
       </c>
-      <c>
+      <c r="L3">
         <v>2.6584461828756458</v>
       </c>
-      <c>
+      <c r="M3">
         <v>2.8329968991051291</v>
       </c>
-      <c>
+      <c r="N3">
         <v>3.0326553867816131</v>
       </c>
-      <c>
+      <c r="O3">
         <v>2.9431463522283514</v>
       </c>
-      <c>
+      <c r="P3">
         <v>3.0393962008846587</v>
       </c>
     </row>
-    <row>
-      <c t="s">
-        <v>16</v>
-      </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-      <c t="s">
-        <v>18</v>
-      </c>
-      <c t="s">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" t="s">
         <v>22</v>
       </c>
-      <c t="s">
-        <v>20</v>
-      </c>
-      <c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4">
         <v>1.3885850146961258</v>
       </c>
-      <c>
+      <c r="G4">
         <v>1.4270430958022244</v>
       </c>
-      <c>
+      <c r="H4">
         <v>1.4076686706032173</v>
       </c>
-      <c>
+      <c r="I4">
         <v>1.3977938493467157</v>
       </c>
-      <c>
+      <c r="J4">
         <v>1.4097383633873699</v>
       </c>
-      <c>
+      <c r="K4">
         <v>1.1823519364537551</v>
       </c>
-      <c>
+      <c r="L4">
         <v>1.309363125155443</v>
       </c>
-      <c>
+      <c r="M4">
         <v>1.4908992873472275</v>
       </c>
-      <c>
+      <c r="N4">
         <v>1.4532616552385635</v>
       </c>
-      <c>
+      <c r="O4">
         <v>1.4423289637669354</v>
       </c>
-      <c>
+      <c r="P4">
         <v>1.012515390584418</v>
       </c>
     </row>
-    <row>
-      <c t="s">
-        <v>16</v>
-      </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-      <c t="s">
-        <v>18</v>
-      </c>
-      <c t="s">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
         <v>23</v>
       </c>
-      <c t="s">
-        <v>20</v>
-      </c>
-      <c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+      <c r="F5">
         <v>8.5203326215774897</v>
       </c>
-      <c>
+      <c r="G5">
         <v>8.4685703254973337</v>
       </c>
-      <c>
+      <c r="H5">
         <v>8.521759239223055</v>
       </c>
-      <c>
+      <c r="I5">
         <v>8.6047380472534076</v>
       </c>
-      <c>
+      <c r="J5">
         <v>8.7314259441946387</v>
       </c>
-      <c>
+      <c r="K5">
         <v>10.007412711486452</v>
       </c>
-      <c>
+      <c r="L5">
         <v>10.62956212878024</v>
       </c>
-      <c>
+      <c r="M5">
         <v>10.712702255527518</v>
       </c>
-      <c>
+      <c r="N5">
         <v>10.312305665206207</v>
       </c>
-      <c>
+      <c r="O5">
         <v>10.360921645304755</v>
       </c>
-      <c>
+      <c r="P5">
         <v>10.748306276699269</v>
       </c>
     </row>
-    <row>
-      <c t="s">
-        <v>16</v>
-      </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-      <c t="s">
-        <v>18</v>
-      </c>
-      <c t="s">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D6" t="s">
         <v>24</v>
       </c>
-      <c t="s">
-        <v>20</v>
-      </c>
-      <c>
+      <c r="E6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6">
         <v>5.0173655672231732</v>
       </c>
-      <c>
+      <c r="G6">
         <v>5.1693922149553746</v>
       </c>
-      <c>
+      <c r="H6">
         <v>5.1224121648451471</v>
       </c>
-      <c>
+      <c r="I6">
         <v>5.2929643668360118</v>
       </c>
-      <c>
+      <c r="J6">
         <v>5.2692770238219433</v>
       </c>
-      <c>
+      <c r="K6">
         <v>4.6270599026630848</v>
       </c>
-      <c>
+      <c r="L6">
         <v>4.9084164359999347</v>
       </c>
-      <c>
+      <c r="M6">
         <v>5.5102712171520505</v>
       </c>
-      <c>
+      <c r="N6">
         <v>5.74468902465492</v>
       </c>
-      <c>
+      <c r="O6">
         <v>5.8192564123059229</v>
       </c>
-      <c>
+      <c r="P6">
         <v>5.8289547171787879</v>
       </c>
     </row>
-    <row>
-      <c t="s">
-        <v>16</v>
-      </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-      <c t="s">
-        <v>18</v>
-      </c>
-      <c t="s">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D7" t="s">
         <v>25</v>
       </c>
-      <c t="s">
-        <v>20</v>
-      </c>
-      <c>
+      <c r="E7" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7">
         <v>0.15331987059857177</v>
       </c>
-      <c>
+      <c r="G7">
         <v>0.13749495079374804</v>
       </c>
-      <c>
+      <c r="H7">
         <v>0.17860032389288841</v>
       </c>
-      <c>
+      <c r="I7">
         <v>0.14367446216312171</v>
       </c>
-      <c>
+      <c r="J7">
         <v>0.11199909449051633</v>
       </c>
-      <c>
+      <c r="K7">
         <v>0.10515336395783935</v>
       </c>
-      <c>
-        <v>0.079943676780994247</v>
-      </c>
-      <c>
-        <v>0.087721770640789551</v>
-      </c>
-      <c>
-        <v>0.093393575367384324</v>
-      </c>
-      <c>
-        <v>0.091483234301906219</v>
-      </c>
-      <c>
+      <c r="L7">
+        <v>7.9943676780994247E-2</v>
+      </c>
+      <c r="M7">
+        <v>8.7721770640789551E-2</v>
+      </c>
+      <c r="N7">
+        <v>9.3393575367384324E-2</v>
+      </c>
+      <c r="O7">
+        <v>9.1483234301906219E-2</v>
+      </c>
+      <c r="P7">
         <v>0.11109225012598054</v>
       </c>
     </row>
-    <row>
-      <c t="s">
-        <v>16</v>
-      </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-      <c t="s">
-        <v>18</v>
-      </c>
-      <c t="s">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" t="s">
         <v>26</v>
       </c>
-      <c t="s">
-        <v>20</v>
-      </c>
-      <c>
+      <c r="E8" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8">
         <v>0.14521026040254639</v>
       </c>
-      <c>
+      <c r="G8">
         <v>0.14831642453977689</v>
       </c>
-      <c>
+      <c r="H8">
         <v>0.13830691478293472</v>
       </c>
-      <c>
+      <c r="I8">
         <v>0.14014428876546389</v>
       </c>
-      <c>
+      <c r="J8">
         <v>0.1414322754331504</v>
       </c>
-      <c>
+      <c r="K8">
         <v>0.17219039462023397</v>
       </c>
-      <c>
+      <c r="L8">
         <v>0.17761561775979773</v>
       </c>
-      <c>
+      <c r="M8">
         <v>0.14058620484226539</v>
       </c>
-      <c>
+      <c r="N8">
         <v>0.13121301141897723</v>
       </c>
-      <c>
+      <c r="O8">
         <v>0.15096028524966965</v>
       </c>
-      <c>
+      <c r="P8">
         <v>0.13106775003488871</v>
       </c>
     </row>
-    <row>
-      <c t="s">
-        <v>16</v>
-      </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-      <c t="s">
-        <v>18</v>
-      </c>
-      <c t="s">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" t="s">
         <v>27</v>
       </c>
-      <c t="s">
-        <v>20</v>
-      </c>
-      <c>
+      <c r="E9" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9">
         <v>1.8870447465157243</v>
       </c>
-      <c>
+      <c r="G9">
         <v>1.7697375360999292</v>
       </c>
-      <c>
+      <c r="H9">
         <v>1.7094515570023601</v>
       </c>
-      <c>
+      <c r="I9">
         <v>1.6417211714654749</v>
       </c>
-      <c>
+      <c r="J9">
         <v>1.674594717777437</v>
       </c>
-      <c>
+      <c r="K9">
         <v>1.4521420502185245</v>
       </c>
-      <c>
+      <c r="L9">
         <v>1.6768070071944485</v>
       </c>
-      <c>
+      <c r="M9">
         <v>1.6145717287207726</v>
       </c>
-      <c>
+      <c r="N9">
         <v>1.7853952470623273</v>
       </c>
-      <c>
+      <c r="O9">
         <v>1.8326455077590826</v>
       </c>
-      <c>
+      <c r="P9">
         <v>1.6619553565462624</v>
       </c>
     </row>
-    <row>
-      <c t="s">
-        <v>16</v>
-      </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-      <c t="s">
-        <v>18</v>
-      </c>
-      <c t="s">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>16</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" t="s">
         <v>28</v>
       </c>
-      <c t="s">
-        <v>20</v>
-      </c>
-      <c>
+      <c r="E10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10">
         <v>2.3761788661176504</v>
       </c>
-      <c>
+      <c r="G10">
         <v>2.4931177994725644</v>
       </c>
-      <c>
+      <c r="H10">
         <v>2.3684538882828106</v>
       </c>
-      <c>
+      <c r="I10">
         <v>2.4439455556653065</v>
       </c>
-      <c>
+      <c r="J10">
         <v>2.5496208937832581</v>
       </c>
-      <c>
+      <c r="K10">
         <v>2.3511963447138635</v>
       </c>
-      <c>
+      <c r="L10">
         <v>2.5677459861181582</v>
       </c>
-      <c>
+      <c r="M10">
         <v>2.6208039317970075</v>
       </c>
-      <c>
+      <c r="N10">
         <v>2.5365643586865279</v>
       </c>
-      <c>
+      <c r="O10">
         <v>2.4501012081366831</v>
       </c>
-      <c>
+      <c r="P10">
         <v>2.5921912315909745</v>
       </c>
     </row>
-    <row>
-      <c t="s">
-        <v>16</v>
-      </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-      <c t="s">
-        <v>18</v>
-      </c>
-      <c t="s">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D11" t="s">
         <v>29</v>
       </c>
-      <c t="s">
-        <v>20</v>
-      </c>
-      <c>
+      <c r="E11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11">
         <v>3.8413155208849603</v>
       </c>
-      <c>
+      <c r="G11">
         <v>3.8711813859186299</v>
       </c>
-      <c>
+      <c r="H11">
         <v>3.9009466720606722</v>
       </c>
-      <c>
+      <c r="I11">
         <v>3.9277460306583025</v>
       </c>
-      <c>
+      <c r="J11">
         <v>3.9917794052252464</v>
       </c>
-      <c>
+      <c r="K11">
         <v>3.7520177571054614</v>
       </c>
-      <c>
+      <c r="L11">
         <v>4.0474846999348983</v>
       </c>
-      <c>
+      <c r="M11">
         <v>4.1423285067323494</v>
       </c>
-      <c>
+      <c r="N11">
         <v>4.0886181200311338</v>
       </c>
-      <c>
+      <c r="O11">
         <v>4.1894816210395787</v>
       </c>
-      <c>
+      <c r="P11">
         <v>4.1689468592060068</v>
       </c>
     </row>
-    <row>
-      <c t="s">
-        <v>16</v>
-      </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-      <c t="s">
-        <v>18</v>
-      </c>
-      <c t="s">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" t="s">
         <v>30</v>
       </c>
-      <c t="s">
-        <v>20</v>
-      </c>
-      <c>
+      <c r="E12" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12">
         <v>0.71834557881788275</v>
       </c>
-      <c>
+      <c r="G12">
         <v>0.71238290359620515</v>
       </c>
-      <c>
+      <c r="H12">
         <v>0.72289881590320171</v>
       </c>
-      <c>
+      <c r="I12">
         <v>0.7332282461893842</v>
       </c>
-      <c>
+      <c r="J12">
         <v>0.73314182604918376</v>
       </c>
-      <c>
+      <c r="K12">
         <v>0.5348139631111235</v>
       </c>
-      <c>
+      <c r="L12">
         <v>0.62192626478347757</v>
       </c>
-      <c>
+      <c r="M12">
         <v>0.63934243669100721</v>
       </c>
-      <c>
+      <c r="N12">
         <v>0.57044631327309581</v>
       </c>
-      <c>
+      <c r="O12">
         <v>0.6207780254860007</v>
       </c>
-      <c>
+      <c r="P12">
         <v>0.90082744476813703</v>
       </c>
     </row>
-    <row>
-      <c t="s">
-        <v>16</v>
-      </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-      <c t="s">
-        <v>18</v>
-      </c>
-      <c t="s">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s">
+        <v>18</v>
+      </c>
+      <c r="D13" t="s">
         <v>31</v>
       </c>
-      <c t="s">
-        <v>20</v>
-      </c>
-      <c>
+      <c r="E13" t="s">
+        <v>20</v>
+      </c>
+      <c r="F13">
         <v>0.52170393697935702</v>
       </c>
-      <c>
+      <c r="G13">
         <v>0.52174424433771638</v>
       </c>
-      <c>
+      <c r="H13">
         <v>0.53997157582448285</v>
       </c>
-      <c>
+      <c r="I13">
         <v>0.55903763141497809</v>
       </c>
-      <c>
+      <c r="J13">
         <v>0.56575017575369368</v>
       </c>
-      <c>
+      <c r="K13">
         <v>0.41092529714089032</v>
       </c>
-      <c>
+      <c r="L13">
         <v>0.4780542985293566</v>
       </c>
-      <c>
+      <c r="M13">
         <v>0.45312009275020104</v>
       </c>
-      <c>
+      <c r="N13">
         <v>0.37494036620783577</v>
       </c>
-      <c>
+      <c r="O13">
         <v>0.40459728651029814</v>
       </c>
-      <c>
+      <c r="P13">
         <v>0.57338868877834459</v>
       </c>
     </row>
-    <row>
-      <c t="s">
-        <v>16</v>
-      </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-      <c t="s">
-        <v>18</v>
-      </c>
-      <c t="s">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>16</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" t="s">
         <v>32</v>
       </c>
-      <c t="s">
-        <v>20</v>
-      </c>
-      <c>
+      <c r="E14" t="s">
+        <v>20</v>
+      </c>
+      <c r="F14">
         <v>1.3607538090932414</v>
       </c>
-      <c>
+      <c r="G14">
         <v>1.2714210568245348</v>
       </c>
-      <c>
+      <c r="H14">
         <v>1.2702377003395651</v>
       </c>
-      <c>
+      <c r="I14">
         <v>1.2841180528844185</v>
       </c>
-      <c>
+      <c r="J14">
         <v>1.3270683163862069</v>
       </c>
-      <c>
+      <c r="K14">
         <v>1.2820283967921458</v>
       </c>
-      <c>
+      <c r="L14">
         <v>1.3384288526849284</v>
       </c>
-      <c>
+      <c r="M14">
         <v>1.4385241145889978</v>
       </c>
-      <c>
+      <c r="N14">
         <v>1.5842635975093367</v>
       </c>
-      <c>
+      <c r="O14">
         <v>1.4548766723540181</v>
       </c>
-      <c>
+      <c r="P14">
         <v>1.5083595207668479</v>
       </c>
     </row>
-    <row>
-      <c t="s">
-        <v>16</v>
-      </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-      <c t="s">
-        <v>18</v>
-      </c>
-      <c t="s">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+      <c r="C15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" t="s">
         <v>33</v>
       </c>
-      <c t="s">
-        <v>20</v>
-      </c>
-      <c>
+      <c r="E15" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15">
         <v>1.4833336899209422</v>
       </c>
-      <c>
+      <c r="G15">
         <v>1.442769571233363</v>
       </c>
-      <c>
+      <c r="H15">
         <v>1.534331240305995</v>
       </c>
-      <c>
+      <c r="I15">
         <v>1.5343868098632814</v>
       </c>
-      <c>
+      <c r="J15">
         <v>1.4838354819030648</v>
       </c>
-      <c>
+      <c r="K15">
         <v>0.74543226690066211</v>
       </c>
-      <c>
+      <c r="L15">
         <v>0.89576586475088837</v>
       </c>
-      <c>
+      <c r="M15">
         <v>0.74834584472998111</v>
       </c>
-      <c>
+      <c r="N15">
         <v>0.80025901055474069</v>
       </c>
-      <c>
+      <c r="O15">
         <v>0.83984525533768195</v>
       </c>
-      <c>
+      <c r="P15">
         <v>0.48951967157186715</v>
       </c>
     </row>
-    <row>
-      <c t="s">
-        <v>16</v>
-      </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-      <c t="s">
-        <v>18</v>
-      </c>
-      <c t="s">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" t="s">
         <v>34</v>
       </c>
-      <c t="s">
-        <v>20</v>
-      </c>
-      <c>
+      <c r="E16" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16">
         <v>5.6907246061034407</v>
       </c>
-      <c>
+      <c r="G16">
         <v>5.6859214265704301</v>
       </c>
-      <c>
+      <c r="H16">
         <v>5.5348316729456268</v>
       </c>
-      <c>
+      <c r="I16">
         <v>5.4414482044098333</v>
       </c>
-      <c>
+      <c r="J16">
         <v>5.2102077298261964</v>
       </c>
-      <c>
+      <c r="K16">
         <v>5.2489621001086517</v>
       </c>
-      <c>
+      <c r="L16">
         <v>5.4007326099166209</v>
       </c>
-      <c>
+      <c r="M16">
         <v>5.1949378513256361</v>
       </c>
-      <c>
+      <c r="N16">
         <v>4.5585730312153521</v>
       </c>
-      <c>
+      <c r="O16">
         <v>4.738193220787652</v>
       </c>
-      <c>
+      <c r="P16">
         <v>4.7863178464651233</v>
       </c>
     </row>
-    <row>
-      <c t="s">
-        <v>16</v>
-      </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-      <c t="s">
-        <v>18</v>
-      </c>
-      <c t="s">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" t="s">
         <v>35</v>
       </c>
-      <c t="s">
-        <v>20</v>
-      </c>
-      <c>
+      <c r="E17" t="s">
+        <v>20</v>
+      </c>
+      <c r="F17">
         <v>2.7206246655086579</v>
       </c>
-      <c>
+      <c r="G17">
         <v>2.7750122842135867</v>
       </c>
-      <c>
+      <c r="H17">
         <v>2.6346204591515994</v>
       </c>
-      <c>
+      <c r="I17">
         <v>2.5967782178490904</v>
       </c>
-      <c>
+      <c r="J17">
         <v>2.5814295577818793</v>
       </c>
-      <c>
+      <c r="K17">
         <v>2.3890295408997</v>
       </c>
-      <c>
+      <c r="L17">
         <v>2.7686359142331929</v>
       </c>
-      <c>
+      <c r="M17">
         <v>2.7612112831668747</v>
       </c>
-      <c>
+      <c r="N17">
         <v>2.6097248932741262</v>
       </c>
-      <c>
+      <c r="O17">
         <v>2.7739836195588077</v>
       </c>
-      <c>
+      <c r="P17">
         <v>2.2754668828586082</v>
       </c>
     </row>
-    <row>
-      <c t="s">
-        <v>16</v>
-      </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-      <c t="s">
-        <v>18</v>
-      </c>
-      <c t="s">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" t="s">
         <v>36</v>
       </c>
-      <c t="s">
-        <v>20</v>
-      </c>
-      <c>
+      <c r="E18" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18">
         <v>10.969000344535704</v>
       </c>
-      <c>
+      <c r="G18">
         <v>10.982040535891947</v>
       </c>
-      <c>
+      <c r="H18">
         <v>11.017483547009</v>
       </c>
-      <c>
+      <c r="I18">
         <v>11.055631387122414</v>
       </c>
-      <c>
+      <c r="J18">
         <v>11.005725239832552</v>
       </c>
-      <c>
+      <c r="K18">
         <v>10.609352853524003</v>
       </c>
-      <c>
+      <c r="L18">
         <v>10.917404609034341</v>
       </c>
-      <c>
+      <c r="M18">
         <v>10.942679779591352</v>
       </c>
-      <c>
+      <c r="N18">
         <v>8.0582547864014078</v>
       </c>
-      <c>
+      <c r="O18">
         <v>10.338995680235014</v>
       </c>
-      <c>
+      <c r="P18">
         <v>10.596045540424619</v>
       </c>
     </row>
-    <row>
-      <c t="s">
-        <v>16</v>
-      </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-      <c t="s">
-        <v>18</v>
-      </c>
-      <c t="s">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" t="s">
         <v>37</v>
       </c>
-      <c t="s">
-        <v>20</v>
-      </c>
-      <c>
+      <c r="E19" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19">
         <v>2.9467268330098633</v>
       </c>
-      <c>
+      <c r="G19">
         <v>2.9462625096460511</v>
       </c>
-      <c>
+      <c r="H19">
         <v>2.8902745826575651</v>
       </c>
-      <c>
+      <c r="I19">
         <v>2.8946873781646816</v>
       </c>
-      <c>
+      <c r="J19">
         <v>2.8183879580902662</v>
       </c>
-      <c>
+      <c r="K19">
         <v>2.6452264890263022</v>
       </c>
-      <c>
+      <c r="L19">
         <v>2.7733901815467417</v>
       </c>
-      <c>
+      <c r="M19">
         <v>2.7918201500261599</v>
       </c>
-      <c>
+      <c r="N19">
         <v>2.4404525283926772</v>
       </c>
-      <c>
+      <c r="O19">
         <v>2.5291712616538318</v>
       </c>
-      <c>
+      <c r="P19">
         <v>2.8597270388925531</v>
       </c>
     </row>
-    <row>
-      <c t="s">
-        <v>16</v>
-      </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-      <c t="s">
-        <v>18</v>
-      </c>
-      <c t="s">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>16</v>
+      </c>
+      <c r="B20" t="s">
+        <v>17</v>
+      </c>
+      <c r="C20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" t="s">
         <v>38</v>
       </c>
-      <c t="s">
-        <v>20</v>
-      </c>
-      <c>
+      <c r="E20" t="s">
+        <v>20</v>
+      </c>
+      <c r="F20">
         <v>0.14933145382973098</v>
       </c>
-      <c>
+      <c r="G20">
         <v>1.7739653373784565</v>
       </c>
-      <c>
+      <c r="H20">
         <v>3.9022246683031536</v>
       </c>
-      <c>
+      <c r="I20">
         <v>4.2374277443985156</v>
       </c>
-      <c>
+      <c r="J20">
         <v>4.8567205187782383</v>
       </c>
-      <c>
-        <v>0.042686598511413681</v>
-      </c>
-      <c>
-        <v>9.6370761981690919E-03</v>
-      </c>
-      <c>
-        <v>0.011671702821623298</v>
-      </c>
-      <c>
-        <v>0.010510449140653555</v>
-      </c>
-      <c>
-        <v>0.02423357836302464</v>
-      </c>
-      <c>
-        <v>0.06245744875078791</v>
-      </c>
-    </row>
-    <row>
-      <c t="s">
-        <v>16</v>
-      </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-      <c t="s">
-        <v>18</v>
-      </c>
-      <c t="s">
+      <c r="K20">
+        <v>4.2686598511413681E-2</v>
+      </c>
+      <c r="L20">
+        <v>9.6370761981690919E-3</v>
+      </c>
+      <c r="M20">
+        <v>1.1671702821623298E-2</v>
+      </c>
+      <c r="N20">
+        <v>1.0510449140653555E-2</v>
+      </c>
+      <c r="O20">
+        <v>2.423357836302464E-2</v>
+      </c>
+      <c r="P20">
+        <v>6.245744875078791E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+      <c r="B21" t="s">
+        <v>17</v>
+      </c>
+      <c r="C21" t="s">
+        <v>18</v>
+      </c>
+      <c r="D21" t="s">
         <v>39</v>
       </c>
-      <c t="s">
-        <v>20</v>
-      </c>
-      <c>
+      <c r="E21" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21">
         <v>1.9135147283233906</v>
       </c>
-      <c>
+      <c r="G21">
         <v>1.9033476205255346</v>
       </c>
-      <c>
+      <c r="H21">
         <v>2.0087426706664564</v>
       </c>
-      <c>
+      <c r="I21">
         <v>2.0296924408243147</v>
       </c>
-      <c>
+      <c r="J21">
         <v>2.1156517702679891</v>
       </c>
-      <c>
+      <c r="K21">
         <v>2.1757705738949129</v>
       </c>
-      <c>
+      <c r="L21">
         <v>2.2547094452621064</v>
       </c>
-      <c>
+      <c r="M21">
         <v>2.1522532694179097</v>
       </c>
-      <c>
+      <c r="N21">
         <v>2.2324884794600646</v>
       </c>
-      <c>
+      <c r="O21">
         <v>2.146926424578135</v>
       </c>
-      <c>
+      <c r="P21">
         <v>2.2985719558878994</v>
       </c>
     </row>
-    <row>
-      <c t="s">
-        <v>16</v>
-      </c>
-      <c t="s">
-        <v>17</v>
-      </c>
-      <c t="s">
-        <v>18</v>
-      </c>
-      <c t="s">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>16</v>
+      </c>
+      <c r="B22" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" t="s">
         <v>40</v>
       </c>
-      <c t="s">
-        <v>20</v>
-      </c>
-      <c>
+      <c r="E22" t="s">
+        <v>20</v>
+      </c>
+      <c r="F22">
         <v>12.728393994816484</v>
       </c>
-      <c>
+      <c r="G22">
         <v>13.003684165434846</v>
       </c>
-      <c>
+      <c r="H22">
         <v>13.053042831038827</v>
       </c>
-      <c>
+      <c r="I22">
         <v>13.03330504839828</v>
       </c>
-      <c>
+      <c r="J22">
         <v>12.948601827252316</v>
       </c>
-      <c>
+      <c r="K22">
         <v>12.723320130705597</v>
       </c>
-      <c>
+      <c r="L22">
         <v>12.929355347933035</v>
       </c>
-      <c>
+      <c r="M22">
         <v>12.882727622641646</v>
       </c>
-      <c>
+      <c r="N22">
         <v>12.67877658939487</v>
       </c>
-      <c>
+      <c r="O22">
         <v>12.640416434655581</v>
       </c>
-      <c>
+      <c r="P22">
         <v>13.277565515267884</v>
       </c>
     </row>
